--- a/data/trans_camb/PCS12_SP_R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,98</t>
+          <t>-2,6; 5,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,95</t>
+          <t>-2,31; 5,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 14,1</t>
+          <t>5,57; 14,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 8,57</t>
+          <t>-0,98; 8,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 7,64</t>
+          <t>-2,14; 7,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,23</t>
+          <t>0,89; 9,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 6,14</t>
+          <t>-0,56; 5,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 5,54</t>
+          <t>-0,78; 5,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 10,68</t>
+          <t>4,26; 10,78</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 38,75</t>
+          <t>-13,6; 36,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 38,79</t>
+          <t>-12,11; 37,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,65; 94,51</t>
+          <t>27,87; 93,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 34,29</t>
+          <t>-3,39; 35,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 30,84</t>
+          <t>-6,74; 31,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 37,8</t>
+          <t>3,27; 38,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 29,93</t>
+          <t>-2,32; 28,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 26,1</t>
+          <t>-3,42; 27,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,17; 52,52</t>
+          <t>17,34; 52,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,78</t>
+          <t>1,01; 7,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,19</t>
+          <t>-0,95; 5,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 50,62</t>
+          <t>3,14; 50,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,28</t>
+          <t>-1,72; 6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,08</t>
+          <t>-5,0; 3,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 6,4</t>
+          <t>-1,04; 6,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,05</t>
+          <t>0,57; 6,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 3,23</t>
+          <t>-1,82; 3,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 33,07</t>
+          <t>2,41; 34,87</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 62,45</t>
+          <t>6,65; 61,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 41,05</t>
+          <t>-6,24; 41,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,39; 381,18</t>
+          <t>21,02; 370,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 25,01</t>
+          <t>-5,91; 26,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 12,3</t>
+          <t>-16,85; 12,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 25,49</t>
+          <t>-3,45; 26,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 31,07</t>
+          <t>2,39; 31,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 16,72</t>
+          <t>-8,14; 16,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,14; 166,81</t>
+          <t>11,24; 170,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 0,88</t>
+          <t>-6,84; 0,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 1,32</t>
+          <t>-6,26; 1,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 7,82</t>
+          <t>-0,7; 7,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,48</t>
+          <t>-7,23; 2,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -1,08</t>
+          <t>-9,82; -0,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -1,03</t>
+          <t>-19,82; -1,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; -0,03</t>
+          <t>-5,82; 0,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,91; -0,96</t>
+          <t>-6,94; -0,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 1,68</t>
+          <t>-10,67; 1,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 5,61</t>
+          <t>-35,94; 6,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 9,08</t>
+          <t>-33,44; 9,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 50,9</t>
+          <t>-4,45; 47,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 5,83</t>
+          <t>-23,76; 9,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,26; -3,96</t>
+          <t>-32,22; -3,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,7; -4,2</t>
+          <t>-63,39; -3,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,45; -0,1</t>
+          <t>-23,75; 1,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,03; -4,65</t>
+          <t>-27,83; -3,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 7,26</t>
+          <t>-43,77; 7,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,32</t>
+          <t>0,4; 7,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 4,71</t>
+          <t>-2,16; 4,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,79</t>
+          <t>2,72; 10,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 7,76</t>
+          <t>-0,22; 7,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,06</t>
+          <t>-4,36; 3,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 8,66</t>
+          <t>-2,03; 8,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,25</t>
+          <t>0,7; 6,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,16</t>
+          <t>-2,03; 2,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,26</t>
+          <t>1,93; 8,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 52,0</t>
+          <t>2,4; 53,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 34,02</t>
+          <t>-13,0; 34,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,74; 71,08</t>
+          <t>16,12; 71,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 32,17</t>
+          <t>-0,94; 31,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 12,45</t>
+          <t>-15,77; 14,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 35,57</t>
+          <t>-7,44; 35,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,57; 32,04</t>
+          <t>3,42; 31,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 16,62</t>
+          <t>-9,23; 14,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,52; 41,29</t>
+          <t>8,72; 41,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,92</t>
+          <t>0,19; 3,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,72</t>
+          <t>-0,84; 2,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,13; 30,73</t>
+          <t>5,02; 26,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,1</t>
+          <t>-0,08; 4,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,98</t>
+          <t>-3,02; 1,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,88</t>
+          <t>-4,18; 3,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,45</t>
+          <t>0,63; 3,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,44</t>
+          <t>-1,45; 1,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 13,98</t>
+          <t>2,64; 15,35</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,82; 26,22</t>
+          <t>1,08; 26,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 18,29</t>
+          <t>-5,02; 18,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31,91; 197,18</t>
+          <t>30,71; 169,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 15,83</t>
+          <t>-0,39; 16,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 3,73</t>
+          <t>-10,76; 4,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 14,6</t>
+          <t>-14,66; 14,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,52; 16,51</t>
+          <t>2,79; 16,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 6,87</t>
+          <t>-6,57; 6,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11,77; 66,1</t>
+          <t>12,12; 71,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,69</t>
+          <t>9,43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>4,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,53</t>
+          <t>7,05</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 5,75</t>
+          <t>-2,21; 5,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 5,92</t>
+          <t>-2,36; 5,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 14,41</t>
+          <t>4,98; 13,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 8,64</t>
+          <t>-1,24; 8,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,54</t>
+          <t>-2,94; 7,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,58</t>
+          <t>0,1; 8,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,97</t>
+          <t>-0,24; 6,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 5,83</t>
+          <t>-0,69; 5,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,78</t>
+          <t>3,56; 9,85</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 36,6</t>
+          <t>-11,38; 36,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 37,84</t>
+          <t>-12,82; 36,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,87; 93,91</t>
+          <t>25,72; 88,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 35,26</t>
+          <t>-3,88; 34,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 31,51</t>
+          <t>-9,76; 30,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 38,79</t>
+          <t>-0,06; 32,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 28,63</t>
+          <t>-1,01; 29,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 27,76</t>
+          <t>-3,24; 27,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,34; 52,39</t>
+          <t>14,67; 47,27</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20,92</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,06</t>
+          <t>3,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,5</t>
+          <t>1,25; 7,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,32</t>
+          <t>-0,86; 5,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 50,77</t>
+          <t>0,71; 7,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 6,68</t>
+          <t>-1,88; 6,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,0</t>
+          <t>-4,96; 3,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,54</t>
+          <t>-0,93; 6,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,07</t>
+          <t>0,37; 6,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,34</t>
+          <t>-2,0; 3,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 34,87</t>
+          <t>0,79; 5,98</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147,09%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 61,46</t>
+          <t>7,29; 62,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 41,46</t>
+          <t>-5,64; 45,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,02; 370,3</t>
+          <t>3,92; 56,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 26,5</t>
+          <t>-6,31; 26,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 12,0</t>
+          <t>-16,85; 13,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 26,64</t>
+          <t>-3,48; 25,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 31,08</t>
+          <t>2,0; 31,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 16,93</t>
+          <t>-9,01; 18,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 170,06</t>
+          <t>3,5; 30,64</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>3,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-8,5</t>
+          <t>-2,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,9</t>
+          <t>-7,05; 0,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 1,37</t>
+          <t>-6,4; 1,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 7,29</t>
+          <t>-1,3; 7,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 2,41</t>
+          <t>-7,57; 1,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -0,85</t>
+          <t>-9,96; -0,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,82; -1,02</t>
+          <t>-6,34; 2,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,25</t>
+          <t>-6,14; 0,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -0,83</t>
+          <t>-7,24; -0,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 1,64</t>
+          <t>-2,59; 3,58</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-29,57%</t>
+          <t>-7,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-11,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 6,61</t>
+          <t>-37,47; 4,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 9,56</t>
+          <t>-32,92; 8,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 47,29</t>
+          <t>-6,82; 46,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 9,7</t>
+          <t>-24,37; 6,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,22; -3,58</t>
+          <t>-32,07; -1,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,39; -3,79</t>
+          <t>-20,17; 9,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 1,27</t>
+          <t>-25,2; 1,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,83; -3,69</t>
+          <t>-29,69; -4,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 7,03</t>
+          <t>-10,6; 16,9</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>6,47</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>6,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 7,31</t>
+          <t>0,31; 7,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 4,77</t>
+          <t>-1,86; 4,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 10,05</t>
+          <t>2,11; 8,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 7,68</t>
+          <t>-0,56; 7,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 3,44</t>
+          <t>-4,65; 3,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 8,89</t>
+          <t>2,8; 10,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,19</t>
+          <t>0,99; 6,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,91</t>
+          <t>-2,4; 2,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,21</t>
+          <t>3,55; 8,76</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,4; 53,05</t>
+          <t>1,36; 52,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 34,55</t>
+          <t>-11,62; 32,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,12; 71,33</t>
+          <t>10,85; 62,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 31,21</t>
+          <t>-1,86; 31,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 14,28</t>
+          <t>-16,56; 14,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 35,94</t>
+          <t>9,92; 42,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 31,29</t>
+          <t>4,24; 31,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 14,66</t>
+          <t>-10,67; 14,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 41,44</t>
+          <t>15,81; 44,53</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>4,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,99</t>
+          <t>0,1; 3,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,78</t>
+          <t>-0,95; 2,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 26,48</t>
+          <t>3,49; 7,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,28</t>
+          <t>-0,31; 4,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,18</t>
+          <t>-3,24; 1,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 3,76</t>
+          <t>1,06; 5,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,53</t>
+          <t>0,59; 3,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,36</t>
+          <t>-1,48; 1,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,64; 15,35</t>
+          <t>2,9; 5,59</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,08; 26,39</t>
+          <t>0,95; 26,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 18,39</t>
+          <t>-5,64; 17,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30,71; 169,54</t>
+          <t>20,55; 47,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 16,33</t>
+          <t>-1,08; 15,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 4,6</t>
+          <t>-11,51; 4,87</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 14,15</t>
+          <t>3,69; 19,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,79; 16,73</t>
+          <t>2,54; 16,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 6,37</t>
+          <t>-6,71; 6,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,12; 71,05</t>
+          <t>12,94; 26,66</t>
         </is>
       </c>
     </row>
